--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_204_Benin.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_204_Benin.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3910ac26e6454b6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R37d5b5b224864947"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R499364744d964812"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rb9ce3a551f9d4c6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1136703265ed4fc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8b1e31f4c44a42de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf5efd072f86f4655"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rf7096ccdb50a420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R3cc09d680e7e43ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R8ad7b13cbda24e5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re93528ccc10e4c05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf7ef2a17a8fb4c73"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ204CommercialTable" displayName="EEZ204CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ204CommercialTable" displayName="EEZ204CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ204FunctionalTable" displayName="EEZ204FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ204FunctionalTable" displayName="EEZ204FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ204ValidationTable" displayName="EEZ204ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ204ValidationTable" displayName="EEZ204ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -7126,7 +7080,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd3b7b225e43472d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa0745a576cf4372"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7136,20 +7090,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7157,552 +7101,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.0000116032</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.91</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>812.8305161640995</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.0000116032</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>812.8305161640995</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$97,A2,'Species'!$U$2:$U$97))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>0.009431435045155279</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.91</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>812.8305161640995</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>0.009431435045155279</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>149.9124923242</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.555588606036035</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>359.40871689790487</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>149.9124923242</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>369.8035434709194</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$97,A3,'Species'!$U$2:$U$97))</x:f>
-        <x:v>55438.17087204617</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.555588606036035</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>359.40871689790487</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>53879.856513207735</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1558.3143588384337</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0289220213208332</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.02892202132083331</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>6766.1208021531</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.90193190432382</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>79.7869574630917</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>6766.1208021531</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>152.47006194525002</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$97,A4,'Species'!$U$2:$U$97))</x:f>
-        <x:v>1031630.857833328</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.90193190432382</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>79.7869574630917</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>539848.1926315293</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>491782.66520179866</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.91096473400155</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.9109647340015501</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.0008354291</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.0008354291</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>114.81536214968827</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$97,A5,'Species'!$U$2:$U$97))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>0.09592009466688814</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>0.09592009466688814</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>25919.544174090704</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.3248156652085306</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>211.25921670708462</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>25919.544174090704</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>262.9431545427476</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$97,A6,'Species'!$U$2:$U$97))</x:f>
-        <x:v>6815366.709445505</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.3248156652085306</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>211.25921670708462</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5475742.59962308</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1339624.109822425</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.2446470200981758</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.2446470200981758</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>38343.563585141404</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6705320093522498</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>468.30846642934927</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>38343.563585141404</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1071.0831515423688</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$97,A7,'Species'!$U$2:$U$97))</x:f>
-        <x:v>41069144.92613846</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6705320093522498</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>468.30846642934927</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>17956615.459993813</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>23112529.466144647</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>2.2871317268912885</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>1.2871317268912885</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.0000928254</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5400000000000005</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>346.736850452532</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.0000928254</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$97,A8,'Species'!$U$2:$U$97))</x:f>
-        <x:v>0.03218598683799643</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5400000000000005</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>346.736850452532</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>0.032185986837996464</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>-3.469446951953614e-17</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>-1.0779371064235427e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3510.0627306585006</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.087996389730353</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1224.6060191303688</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3510.0627306585006</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1404.2911666018822</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$97,A9,'Species'!$U$2:$U$97))</x:f>
-        <x:v>4929150.086882214</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.087996389730353</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1224.6060191303688</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>4298443.947489578</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>630706.1393926358</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.146728943565959</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.14672894356595886</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>9298.438824361298</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.423026150603514</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2648.659620168557</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>9298.438824361298</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2649.6100429528105</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$97,A10,'Species'!$U$2:$U$97))</x:f>
-        <x:v>24637236.892810017</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.423026150603514</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2648.659620168557</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>24628399.444693357</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>8837.448116660118</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.000358831605623</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0003588316056228457</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc46b56ac3de9441c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b6d4f2631844a76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7712,20 +7297,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7733,1092 +7308,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4.564167924</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9834350261342393</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>962.5759932709766</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4.564167924</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1062.7667694730467</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$97,A2,'Species'!$U$2:$U$97))</x:f>
-        <x:v>4850.645999921982</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9834350261342393</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>962.5759932709766</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4393.358472899831</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>457.28752702215115</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1040860949187055</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.10408609491870556</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>950.5952111048999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.32278027711236</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2102.7143429843804</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>950.5952111048999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2403.032431990866</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$97,A3,'Species'!$U$2:$U$97))</x:f>
-        <x:v>2284311.1219802783</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.32278027711236</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2102.7143429843804</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1998830.1847625382</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>285480.9372177401</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1428240074589704</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.14282400745897048</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>4234.6532672812</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.7937845318170247</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>621.991617524236</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>4234.6532672812</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>623.5911904281274</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$97,A4,'Species'!$U$2:$U$97))</x:f>
-        <x:v>2640692.471994243</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.7937845318170247</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>621.991617524236</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2633918.8353705243</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>6773.636623718776</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0025716952750239</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0025716952750238792</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>17366.718688795</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.393998568693968</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2477.4138927971226</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>17366.718688795</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2494.0128014883276</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$97,A5,'Species'!$U$2:$U$97))</x:f>
-        <x:v>43312818.72970132</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.393998568693968</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2477.4138927971226</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>43024550.15192016</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>288268.5777811557</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0067000951029883</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0067000951029883215</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>742.7031277058</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.681428998054196</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>480.20756563672074</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>742.7031277058</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>614.1331117530393</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$97,A6,'Species'!$U$2:$U$97))</x:f>
-        <x:v>456118.5829266779</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.681428998054196</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>480.20756563672074</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>356651.6609463807</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>99466.9219802972</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.2788909540372255</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.2788909540372255</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5065.5413038569</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.467023355497854</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>29.310508671276516</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5065.5413038569</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>69.33270383687851</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$97,A7,'Species'!$U$2:$U$97))</x:f>
-        <x:v>351207.67499378585</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.467023355497854</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>29.310508671276516</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>148473.59231140703</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>202734.08268237882</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>2.3654554963361187</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>1.3654554963361187</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2708.2929362861</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.211005926738301</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1625.5709394719247</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2708.2929362861</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1643.6869268746689</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$97,A8,'Species'!$U$2:$U$97))</x:f>
-        <x:v>4451585.693520473</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.211005926738301</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1625.5709394719247</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4402522.292803773</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>49063.40071670059</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0111443843900343</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.011144384390034347</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.0000928254</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.5400000000000005</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>346.736850452532</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.0000928254</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$97,A9,'Species'!$U$2:$U$97))</x:f>
-        <x:v>0.03218598683799643</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.5400000000000005</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>346.736850452532</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>0.032185986837996464</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>-3.469446951953614e-17</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>-1.0779371064235427e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.0000116032</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.0000116032</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$97,A10,'Species'!$U$2:$U$97))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>0.013950114687752768</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>0.013950114687752768</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2041.0146538962</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.928295831824218</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>847.8047233752917</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2041.0146538962</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1034.201069687557</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$97,A11,'Species'!$U$2:$U$97))</x:f>
-        <x:v>2110819.538307429</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.928295831824218</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>847.8047233752917</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1730381.8640513844</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>380437.67425604444</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2198576407668285</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.21985764076682857</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>29843.0545776992</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.341261320298741</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>219.41247699262036</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>29843.0545776992</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>230.95662456080234</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$97,A12,'Species'!$U$2:$U$97))</x:f>
-        <x:v>6892451.1518492075</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.341261320298741</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>219.41247699262036</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>6547938.525918939</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>344512.6259302683</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0526139065854958</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.05261390658549583</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>14386.089252817103</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.61819660788827</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>415.1419375095351</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>14386.089252817103</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>955.0063395727129</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$97,A13,'Species'!$U$2:$U$97))</x:f>
-        <x:v>13738806.438099205</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.61819660788827</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>415.1419375095351</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>5972268.965599593</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>7766537.472499613</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>2.300433305538489</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>1.3004333055384893</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1610.6055926607</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.065508117080563</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1162.8082839995352</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1610.6055926607</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1195.3430560835395</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$97,A14,'Species'!$U$2:$U$97))</x:f>
-        <x:v>1925226.2112762816</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.065508117080563</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1162.8082839995352</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1872825.525401843</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>52400.68587443861</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0279794808238718</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.02797948082387186</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>0.0008354291</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>0.0008354291</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>114.81536214968827</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$97,A15,'Species'!$U$2:$U$97))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>0.09592009466688814</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>0.09592009466688814</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>3676.6539409941</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.462248023209906</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>28.989987173944883</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>3676.6539409941</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>52.80603125625324</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$97,A16,'Species'!$U$2:$U$97))</x:f>
-        <x:v>194149.5029265611</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.462248023209906</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>28.989987173944883</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>106586.15059245288</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>87563.35233410823</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.821526547749332</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.8215265477493321</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>1103.9871354144</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.8633435981962108</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>73.00348591966635</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>1103.9871354144</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>83.6542104900109</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$97,A17,'Species'!$U$2:$U$97))</x:f>
-        <x:v>92353.17220422038</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.8633435981962108</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>73.00348591966635</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>80594.90929571794</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>11758.262908502438</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.145893369832568</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.14589336983256787</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>44.1895933028</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>44.1895933028</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$97,A18,'Species'!$U$2:$U$97))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>5692.7223761834</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>5692.7223761834</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>149.9124923242</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.555588606036035</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>359.40871689790487</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>149.9124923242</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>369.8035434709194</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$97,A19,'Species'!$U$2:$U$97))</x:f>
-        <x:v>55438.17087204617</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.555588606036035</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>359.40871689790487</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>53879.856513207735</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>1558.3143588384337</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0289220213208332</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.02892202132083331</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>59.0666666666</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.56</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>363.0780547701014</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>59.0666666666</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>363.0780547701014</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$97,A20,'Species'!$U$2:$U$97))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>21445.81043506312</x:v>
       </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.56</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>363.0780547701014</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>21445.81043506312</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe5b6d73877f4960"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17fd13fc38494659"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8993,7 +7859,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9092,7 +7958,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>78537967.78151909</x:v>
+        <x:v>52952929.63848208</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9106,7 +7972,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>78537967.78151909</x:v>
+        <x:v>68960954.54882826</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9120,7 +7986,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-25585038.143037006</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9134,7 +8000,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-9577013.232690826</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9145,9 +8011,9 @@
         <x:v>EEZ_204</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9159,47 +8025,19 @@
         <x:v>EEZ_204</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_204</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_204</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9b0913e312d4dba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re11b0e793be043f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9246,7 +8084,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
